--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -573,18 +573,66 @@
           <t>FOUND-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>19 new files under apps/api/src (app.ts; config/env.ts, config/env.test.ts; lib/http-errors.ts, lib/logger.ts, lib/response.ts; middleware/error-handler.ts + .test.ts, not-found.ts, rate-limit.ts + .test.ts, request-context.ts, request-logger.ts; modules/README.md; routes/v1/health.route.ts + .test.ts, routes/v1/index.ts; types/express.d.ts) plus apps/api/tsconfig.build.json.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>apps/api/package.json (ESM, new deps/scripts), apps/api/tsconfig.json (NodeNext), apps/api/.env.example (new vars), apps/api/src/index.ts (replaced placeholder), root package.json (test script), package-lock.json, packages/config/eslint/base.mjs (no-unused-vars underscore-prefix allowance).</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Introduces GET /api/v1/health (liveness only, no DB/Redis dependency) and the standardized success/error response envelope used by all future endpoints. 404, validation, rate-limit, and internal errors all use the standardized error envelope.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>None. No MongoDB/Mongoose code. Deferred to DB-001.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>helmet() security headers; CORS restricted to a configured allowlist, fails fast at startup in production if CORS_ORIGIN is missing or '*'; 1MB JSON body limit; X-Request-Id on every request/response; pino log redaction for Authorization/Cookie/Set-Cookie headers; in-memory rate-limit foundation (documented single-instance-only, not yet wired to any route); centralized error handler that never leaks stack traces or internals to clients.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9 tests across 4 files: config/env.test.ts (4: dev defaults, prod fails fast without CORS_ORIGIN, prod fails fast with CORS_ORIGIN=*, prod succeeds with a valid origin), routes/v1/health.route.test.ts (2: health envelope, 404 envelope), middleware/error-handler.test.ts (2: AppError mapping with no stack-trace leak, unknown error maps to 500 with no message leak), middleware/rate-limit.test.ts (1: blocks after threshold).</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>npm install: 124 packages added, 0 vulnerabilities. npm run typecheck: pass (4/4 workspaces). npm run lint: pass (4/4, after one shared-config fix). npm run format:check: pass. npm run build: pass (4/4). npm run test: pass, 9/9. A manual end-to-end HTTP smoke test against the compiled server was attempted but blocked by this development sandbox's socket-listen permissions (confirmed via a minimal bare-HTTP-server reproduction returning EACCES - not a code defect); the automated tests already exercise real HTTP request/response cycles through the Express app via supertest.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>f0ff3a46bfc30b95aef0b6b0cf42d7e9adca4635</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>In-memory rate limiter is single-instance only; a Redis-backed store is deferred until distributed deployment/Redis infrastructure exists (documented in code). TypeScript remains pinned to 6.0.3 (not registry latest 7.0.2) per the FOUND-001 typescript-eslint compatibility finding. Live process-level SIGTERM/SIGINT behavior was not exercised end-to-end in this environment due to sandboxed socket permissions blocking a real bound listener from outside its own process; the shutdown logic was verified by code review against Node’s documented server.close() API and is standard, well-established practice.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Implements FOUND-002 per the approved final plan (architecture decision round, adjustments round, final file-by-file plan). Two real API-shape issues were found and fixed during implementation, not assumed: pino-http requires the named `pinoHttp` import (its default import has no call signatures under NodeNext module resolution), and the test script must invoke `tsx --test` with no directory argument (passing `src` gets resolved as a module specifier to src/index.ts and executes it directly - including binding a real port - instead of recursively discovering *.test.ts files).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -640,18 +640,66 @@
           <t>DB-001</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>apps/api/src/db/{README.md, connection.ts, connection.test.ts, transaction.ts, transaction.test.ts, plugins/default-query-timeout.ts, plugins/default-query-timeout.test.ts}; apps/api/src/routes/v1/{ready.route.ts, ready.route.test.ts}.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>apps/api/src/config/env.ts (Mongo env vars + production TLS/localhost guards), apps/api/src/config/env.test.ts, apps/api/src/index.ts (connect before listen, disconnect in shutdown), apps/api/src/lib/http-errors.ts (NOT_READY code), apps/api/src/routes/v1/{index.ts,health.route.test.ts}, apps/api/package.json, apps/api/.env.example, package-lock.json.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Adds GET /api/v1/ready (reflects real MongoDB connection state, 503 when not ready, standard envelope). No other route changes; /api/v1/health remains liveness-only.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Establishes the singleton Mongoose connection, connection lifecycle, retry-bounded initial connect, global maxTimeMS plugin, and a MongoDB-only withTransaction() helper. No business schemas, no indexes (none needed yet) - conventions documented in db/README.md for future modules.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Production startup fails fast if MONGODB_URI points at localhost/127.0.0.1, or lacks TLS indication (mongodb+srv:// or explicit tls=true/ssl=true) - a startup safety guard, not a substitute for infrastructure-level TLS. sanitizeFilter and strictQuery enabled platform-wide (NoSQL/operator-injection mitigation, CLAUDE.md section 10). Connection string/credentials are never logged - verified by a dedicated test. autoIndex/autoCreate disabled in production.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14 new tests using mongodb-memory-server: connection.test.ts (3 - connect/disconnect lifecycle, bounded retry gives up against an unreachable host, log output never contains the connection string), default-query-timeout.test.ts (2 - default maxTimeMS applied, explicit override respected), transaction.test.ts (2 - commit and rollback, using MongoMemoryReplSet since transactions require a replica set), ready.route.test.ts (2 - 503 when not connected, 200 when connected), env.test.ts (5 new - localhost rejected, 127.0.0.1 rejected, non-TLS/non-srv rejected, explicit tls=true accepted, mongodb+srv:// accepted). 2 existing FOUND-002 test files updated for the now-required MONGODB_URI/MONGODB_DB_NAME.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>npm install: 50 packages added, 0 vulnerabilities (mongodb-memory-server postinstall script blocked by npm allowScripts, same as esbuild in FOUND-002 - binary downloads lazily on first use instead, confirmed working). npm run typecheck: pass (4/4 workspaces, after fixing a real Mongoose 9 API mismatch - see Known Issues). npm run lint: pass. npm run format:check: pass. npm run build: pass; dist/ confirmed free of compiled test files. npm run test: pass, 23/23 (9 env + 3 connection + 2 timeout-plugin + 2 transaction + 2 error-handler + 1 rate-limit + 2 health + 2 ready).</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0ce5ed8786eebcefa7e37316d2d9f0b5c419745e</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Mongoose 9's schema.pre() middleware dropped the old callback-style next() parameter entirely (now (this, opts?) =&gt; void|Promise&lt;void&gt;) - the initial plugin implementation assumed the older API and failed typecheck; fixed by removing the next() call. Migration tool choice deliberately deferred - recorded as DEC-006 in OPEN_DECISIONS.md, not resolved. Rate limiter (from FOUND-002) remains in-memory/single-instance, unrelated to this task. No generic BaseRepository created, as instructed - concrete repositories arrive per-module when real schemas exist.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Implements DB-001 per the approved final plan, including both explicitly requested confirmations (GET /api/v1/ready implemented; production TLS/localhost safety guard kept) and the withTransaction() scope guard (MongoDB-only, does not imply atomicity for payment/email/SMS/webhook side effects - stated prominently in its own doc comment). No CAT-001 or other business schemas, no auth/RBAC, no Redis started.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -764,18 +764,66 @@
           <t>CAT-001</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/catalog/{README.md, lib/slugify.ts, lib/slugify.test.ts, models/category.model.ts, repositories/category.repository.ts, repositories/category.repository.test.ts, services/category.service.ts, services/category.service.test.ts, validation/category.schema.ts, validation/common.schema.ts} (10 files, all new).</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>None. No existing FOUND-001/002/DB-001 file was modified - the catalog module is fully additive.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>None. No HTTP routes/controllers were created. SEC-001/SEC-002 (authentication, organizations, RBAC) are NOT_STARTED, so there is no authenticated request context to enforce checks at an HTTP boundary; adding routes now would mean either an unauthenticated catalog API or an invented placeholder auth system, both explicitly disallowed. CAT-001 stops at Service -&gt; Repository -&gt; Model; the route layer is deferred until SEC-002 exists.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Category collection only (organizationId, name, slug, description, parentId, status, sortOrder, timestamps). No Brand/Product/ProductVariant schemas - those are CAT-002/003/004. Indexes: {organizationId, slug} unique, {organizationId, parentId, sortOrder}.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Every repository function requires organizationId as a mandatory parameter (the IDOR/tenant-isolation control) - verified by cross-organization-isolation tests. Cross-organization and non-existent parentId both rejected by the service (never trusts a syntactically valid ObjectId as proof of ownership). Hierarchy cycles and self-parenting rejected via a bounded parent-chain walk. Archived categories cannot become new parents. Strict, allowlisted Zod validation - organizationId/_id/__v/createdAt/updatedAt are never client-settable. Slug uniqueness enforced by a real database unique index, not only an application-level check (verified by a concurrent-create race test); the ObjectId validator explicitly rejects the 12-character-string false positive that mongoose.Types.ObjectId.isValid alone would accept.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>38 new tests: slugify.test.ts (7), category.repository.test.ts (12 - org isolation, findById/findBySlug scoping, findChildren ordering, root-category query with parentId both explicitly null and entirely absent, real duplicate-key rejection, cross-org same-slug allowed, concurrent-create race, archived-still-queryable, organizationId immutable on update, index existence/uniqueness), category.service.test.ts (19 - creation, auto-slug generation and collision suffixing, explicit duplicate slug rejected, cross-org/missing/archived parent rejected, self-parent and cycle rejected, valid hierarchy update, archive behavior and no-cascade, NotFoundError paths, strict-schema rejection, malformed ObjectId, allowlisted-update-only, pagination bounds, ObjectId 12-char false-positive guard). All using mongodb-memory-server (MongoMemoryServer - no transactions needed for category CRUD).</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>npm run typecheck: pass (4/4 workspaces, after fixing one real implicit-any on a lean() query result inside the cycle-detection walk). npm run lint: pass. npm run format:check: pass. npm run build: pass. npm run test: 61/61 pass (23 pre-existing + 38 new) - test discovery verified genuine (exact expected count, no duplication, no false positive) rather than assumed. One real test bug found and fixed (a test asserted the wrong default status) and one real Mongoose 9 deprecation fixed (findOneAndUpdate's `new: true` -&gt; `returnDocument: 'after'`) before the suite was clean.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>b332de98c3133920a0c0626efb18309e6a2af2f3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>HTTP routes/controllers, and therefore the "authorization" and "tests pass" parts of the original acceptance-criteria wording that imply an HTTP layer, are deferred until SEC-002 exists - this was explicitly approved scope, not an oversight. No slug-history/redirect tracking. No cascade-archive convenience operation (children keep independent status by design). Concurrency relies on Mongoose's default versionKey; no custom optimistic-concurrency field.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Implements CAT-001 as Category-only, per explicit developer correction: the original broader Product/Variant/Category/Brand foundation proposal was rejected in favor of keeping MASTER_TASK_LIST.xlsx task boundaries (CAT-001=Categories, CAT-002=Brands, CAT-003=Products, CAT-004=Variants) fully intact. No roadmap wording was changed for CAT-001, CAT-002, CAT-003, or CAT-004.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -831,18 +831,66 @@
           <t>CAT-002</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/catalog/{lib/mongo-errors.ts, lib/mongo-errors.test.ts, models/brand.model.ts, repositories/brand.repository.ts, repositories/brand.repository.test.ts, services/brand.service.ts, services/brand.service.test.ts, validation/brand.schema.ts} (8 files, all new).</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/catalog/README.md (added Brand section); apps/api/src/modules/catalog/repositories/category.repository.ts (the one required, approved modification - extracted the model-agnostic isDuplicateKeyError() check into the new shared lib/mongo-errors.ts; Category behavior, error messages and existing tests unchanged).</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>None. No HTTP routes/controllers were created - same SEC-001/SEC-002 dependency reasoning as CAT-001. CAT-002 stops at Service -&gt; Repository -&gt; Model.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Brand collection only (organizationId, name, slug, description, logo {url, altText?}, status, timestamps). No parentId/sortOrder - Brand has no hierarchy, unlike Category. Index: {organizationId, slug} unique only; {organizationId, status} deliberately not added (no current query pattern needs it).</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Every repository function requires organizationId as a mandatory parameter, verified by cross-organization isolation tests covering findById, findBySlug, list, update, and archive. Cross-organization update/archive attempts return null rather than mutating another organization's brand. Strict, allowlisted Zod validation - organizationId/_id/__v/createdAt/updatedAt never client-settable. Slug uniqueness enforced by the real database unique index (verified by a concurrent-create race test), reusing the same lib/slugify.ts and validation/common.schema.ts as Category unchanged.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>29 new tests: lib/mongo-errors.test.ts (3 - recognizes code 11000, rejects unrelated errors, handles non-object input safely), brand.repository.test.ts (13 - create, org isolation, findById/findBySlug/list isolation, duplicate slug at DB level, same slug across orgs, concurrent-create race, organizationId immutable on update, cross-org update/archive no-ops, archived-still-queryable, index existence/uniqueness), brand.service.test.ts (13 - auto slug generation, collision suffixing, explicit duplicate rejected, rename preserves slug, archive behavior, NotFoundError for missing/cross-org id, strict-schema rejection, invalid logo URL, invalid status, partial-update-preserves-fields, valid logo persisted). All using mongodb-memory-server (MongoMemoryServer - no transactions needed).</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>npm install: 0 new packages (no new dependencies). npm run typecheck: pass (4/4 workspaces) on first attempt. npm run lint: pass on first attempt. npm run format:check: pass after auto-format (new files only). npm run build: pass. npm run test: 90/90 pass (61 pre-existing + 29 new) on first attempt - confirmed genuine discovery (exact expected count). All existing CAT-001 tests remain green after the mongo-errors extraction, confirming Category behavior is unchanged.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>92af3b679a5bbfe2dbe08719d1161cfc755ebe12</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>HTTP routes/controllers and the HTTP-authorization portion of the original acceptance-criteria wording remain deferred until SEC-002 exists, same as CAT-001 - explicitly approved scope, not an oversight. No {organizationId, status} index yet - deferred, cheap to add later. Brand status enum is intentionally duplicated locally (validation/brand.schema.ts) rather than sharing a common catalog-status enum with Category, per explicit developer decision not to modify Category's schema file beyond the approved mongo-errors extraction.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Implements CAT-002 (Brand foundation) per the approved plan, including the one required adjustment: extracting isDuplicateKeyError() from category.repository.ts into a shared apps/api/src/modules/catalog/lib/mongo-errors.ts, now used by both category.repository.ts and brand.repository.ts. This is the only intentional modification to a CAT-001 file - verified via git diff to contain only the extraction (one import added, one function/constant removed, nothing else). No Product/ProductVariant, no CAT-003/CAT-004 changes, no roadmap wording changed.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -707,18 +707,66 @@
           <t>SEC-001</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/auth/{README.md, models/user.model.ts, models/security-session.model.ts, models/login-attempt.model.ts, repositories/user.repository.ts+test, repositories/security-session.repository.ts+test, repositories/login-attempt.repository.ts+test, services/password.service.ts+test, services/token.service.ts+test, services/auth.service.ts+test, validation/auth.schema.ts, routes/auth.route.ts+test}; apps/api/src/middleware/{authenticate.ts+test, csrf.ts+test}; apps/api/src/lib/cookies.ts+test (24 new files).</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>apps/api/src/config/env.ts (+auth env vars/config), apps/api/src/lib/http-errors.ts (+UNAUTHENTICATED/UnauthenticatedError), apps/api/src/types/express.d.ts (+req.auth), apps/api/src/app.ts and routes/v1/index.ts (mount /api/v1/auth), apps/api/package.json (+3 deps), apps/api/.env.example (+auth vars documented), package-lock.json. Also apps/api/src/config/env.test.ts, src/db/connection.test.ts, src/routes/v1/{health.route.test.ts,ready.route.test.ts} - each updated only to supply the now-required JWT_ACCESS_TOKEN_SECRET in their local test config, a direct and unavoidable consequence of that field becoming required; no other change to those files.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Adds POST /api/v1/auth/{register,login,logout,refresh}, GET /api/v1/auth/sessions, POST /api/v1/auth/sessions/:id/revoke, POST /api/v1/auth/sessions/revoke-others. All responses use the standard envelope; all failure modes return generic, non-enumerating errors.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Three new collections: User ({email} unique), SecuritySession ({refreshTokenHash} unique, {userId,status}, {familyId}, {expiresAt} TTL), LoginAttempt ({email,createdAt desc}, {createdAt} TTL 90 days). No changes to any CAT-001/CAT-002 schema.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hybrid auth: short-lived stateless JWT access token (jose, HS256, explicit alg/iss/aud allowlist, 15min default) + DB-backed opaque rotating refresh token (SecuritySession, SHA-256 hash at rest). Refresh rotation uses an atomic findOneAndUpdate compare-and-swap (filter includes status:ACTIVE) - not read-then-write - so a race between two concurrent refresh attempts can only let one succeed; the loser triggers family-wide revocation (reuse detection), proven by a dedicated concurrency test. Absolute session lifetime (90 days) bounds the 30-day sliding refresh window regardless of activity. Registration always hashes the password and never authenticates the caller, including for a duplicate email (no enumeration via body/status/cookies/timing). Login failures use progressive doubling delay after a grace period, never a hard lockout, alongside the existing IP rate limiter. Cookies: access_token (path=/), refresh_token (path=/api/v1/auth only), xsrf_token (non-HttpOnly, for double-submit) - all HttpOnly-as-appropriate/Secure-in-production/SameSite=Lax. CSRF: double-submit cookie plus Origin (Referer fallback) validation, applied only to logout/refresh/sessions:id:revoke/revoke-others, never to login/register. authenticate() verifies the JWT cryptographically only - no per-request MongoDB lookup - documented as intentional given the short access-token TTL.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>103 new tests: password.service.test.ts (4), token.service.test.ts (11), user.repository.test.ts (8), security-session.repository.test.ts (10), login-attempt.repository.test.ts (3), auth.service.test.ts (24, including the required CONCURRENCY test proving exactly one of two simultaneous refresh attempts succeeds with no duplicate replacement session), authenticate.test.ts (11), csrf.test.ts (9), cookies.test.ts (8), auth.route.test.ts (15, supertest end-to-end: cookies, CSRF enforcement, Origin validation, refresh rotation, cross-user session isolation). All using mongodb-memory-server (MongoMemoryServer, no transactions needed for this domain).</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>npm install: 3 new packages added (jose 6.2.12, @node-rs/argon2 2.2.1, cookie 2.0.1 - all pre-verified against the plan), 0 vulnerabilities. npm run typecheck: pass (after fixing two real strict-cast errors in pre-existing test files and one real cookie@2.x export-rename issue - see Known Issues). npm run lint: pass. npm run format:check: pass after auto-format (new files only). npm run build: pass. npm run test: 193/193 pass (90 pre-existing + 103 new) - confirmed genuine discovery (24 test files, exact expected count, no false positive) rather than assumed.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>aaffd29</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Immediate session-revocation enforcement and step-up re-authentication for sensitive operations are explicitly deferred to future middleware layered on top of authenticate() - a revoked session's already-issued access token remains valid until its own short natural expiry. RBAC/permissions/organization membership, MFA, password reset, email verification, GeoIP, Redis, and the SEC-003 audit/security-event framework are all explicitly out of scope, per the approved plan. In the true concurrent-refresh race, whether the loser's family-wide revocation also catches the winner's brand-new replacement session is itself racy (a documented, accepted edge case) - the guaranteed invariant is that at most one valid session ever exists from a given rotation and exactly one replacement is ever created.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Implements SEC-001 (Authentication foundation) per the approved revised plan: atomic refresh rotation (not read-then-write) with a dedicated concurrency test, familyId-only session grouping (no parentSessionId), absolute + sliding session expiry, non-enumerating registration, progressive login-delay instead of a hard lockout, LoginAttempt as a minimal SEC-001-scoped model with a 90-day TTL, local-to-auth ObjectId validation (not shared with catalog), the cookie package used directly (Express 5.2.1 verified not to parse request cookies itself; cookie@2.x export rename from parse/serialize to parseCookie/stringifyCookie discovered and fixed during implementation, not assumed), and authenticate() documented as stateless-only by design. No modification to any apps/api/src/modules/catalog/ file - verified via git diff before committing. Nothing pushed to any remote.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -774,18 +774,66 @@
           <t>SEC-002</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/organizations/{README.md, models/organization.model.ts, models/organization-membership.model.ts, repositories/organization.repository.ts+test, repositories/organization-membership.repository.ts+test, authorization/permissions.ts, authorization/policy.ts+test, types/express.d.ts, validation/organization.schema.ts, services/organization.service.ts+test, services/membership.service.ts+test, services/last-owner-protection.test.ts, routes/organization.route.ts+test} (21 new files).</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>apps/api/src/lib/http-errors.ts (+FORBIDDEN error code, +ForbiddenError), apps/api/src/routes/v1/index.ts (mount /api/v1/organizations). No other existing file modified - confirmed via git diff that modules/auth, modules/catalog, db/, middleware/authenticate.ts, middleware/csrf.ts, and types/express.d.ts (SEC-001) are all untouched.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Adds POST/GET /api/v1/organizations, GET/PATCH /api/v1/organizations/:organizationId, and GET/POST /api/v1/organizations/:organizationId/memberships plus PATCH/DELETE .../memberships/:membershipId. All gated by the approved OWNER/ADMIN/MEMBER permission matrix; all responses use the standard envelope; all authorization failures return a single generic 403 (no organization-existence/suspension/membership enumeration).</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Two new collections: Organization ({name, status, activeOwnerCount}, no custom index) and OrganizationMembership ({organizationId, userId, role, status} with a partial-unique index on {organizationId,userId} scoped to status:ACTIVE, plus {userId,status} and {organizationId,role,status}). No change to any existing collection or index.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Organization-context resolved fresh per request from the untrusted URL :organizationId - resolveOrganizationContext() validates the ObjectId, loads the Organization, verifies ACTIVE status, then verifies an ACTIVE membership, attaching req.membership only after all three checks pass. The three distinct failure reasons (org missing, org suspended, not a member) produce a byte-identical generic 403 - verified by a dedicated test. Roles/permissions are a fixed enum + static in-code map (no Role/Permission collections). Last-owner protection uses an atomic, guarded Organization.activeOwnerCount counter (findOneAndUpdate with the count in the filter) rather than count-then-act, which a dedicated concurrency test proves correctly rejects the true write-skew race (two concurrent operations targeting two different owners of the same two-owner organization) - exactly one succeeds, the organization never reaches zero ACTIVE owners. Organization creation and the first OWNER membership are one atomic withTransaction() unit, with a dedicated rollback test proving no orphan Organization survives a forced membership-creation failure. Membership creation is mass-assignment-proof: the endpoint accepts only {userId}, and the service function has no role/status parameter in its signature at all.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>71 new tests: organization.repository.test.ts (9), organization-membership.repository.test.ts (11, including the partial-index and re-add-after-removal behavior), policy.test.ts (12, including the byte-identical-error-response test), organization.service.test.ts (7, including the atomic-bootstrap rollback test), membership.service.test.ts (13, including last-owner Cases A-D and self-management edge cases), last-owner-protection.test.ts (3, including the Case E true-concurrency write-skew test using Promise.allSettled), organization.route.test.ts (16, end-to-end supertest coverage of the full permission matrix, suspension, mass-assignment, and cross-organization IDOR). All transaction-dependent tests use mongodb-memory-server's MongoMemoryReplSet; single-document-atomic-operation tests use a standalone MongoMemoryServer with a plain non-transactional session.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>npm install: 0 new packages (no new dependencies, as required). npm run typecheck: pass (after fixing two real issues found during implementation - see Known Issues). npm run lint: pass. npm run format:check: pass after auto-format (new files only). npm run build: pass. npm run test: 264/264 pass (193 pre-existing + 71 new) - confirmed genuine discovery (31 test files, exact expected count) and zero regression in SEC-001/CAT-001/CAT-002/DB-001/FOUND-002.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>358b2e2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>By design, once an organization is SUSPENDED it cannot be reactivated through any SEC-002 endpoint, including by its own OWNER - there is no platform-admin capability in this task to provide an escape hatch; this was explicitly instructed, not an oversight. Catalog remains completely unauthorized and routeless - SEC-002 builds the reusable authorization mechanism but does not wire it into catalog, since catalog has no route layer yet. No Role/Permission collection, no dynamic/custom roles, no organization-invitation-by-email workflow, no SEC-003 audit persistence (only minimal logger.info lines).</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Implements SEC-002 (Organizations, memberships, roles and permissions) per the twice-revised, fully approved plan: atomic org+first-owner-membership bootstrap (rollback-tested), atomic-counter last-owner protection (concurrency-tested against the true write-skew race, not just a same-document race), the exact approved OWNER/ADMIN/MEMBER permission matrix, URL-based organization context re-verified on every request with no JWT/session changes, a partial (not blanket) unique index enabling re-add-after-removal, and req.membership added via a new declaration-merging file rather than editing SEC-001's types/express.d.ts. No modification to modules/auth or modules/catalog. Nothing pushed to any remote.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -841,18 +841,66 @@
           <t>SEC-003</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/audit/{README.md, models/audit-event.model.ts, repositories/audit-event.repository.ts+test, services/audit.service.ts+test} (6 new files).</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/auth/services/auth.service.ts (+optional trailing logger? param on register/login/logoutCurrentSession/revokeSession/revokeOtherSessions, +13 audit.record() calls across all reachable branches), apps/api/src/modules/auth/routes/auth.route.ts (5 one-line call-site edits passing options.logger through), apps/api/src/modules/organizations/services/organization.service.ts (+audit.record() in createOrganization post-transaction and updateOrganization SUSPENDED branch only), apps/api/src/modules/organizations/services/membership.service.ts (+audit.record() in addMember, changeRole post-transaction, removeMember post-transaction). Additive test-only changes to auth.service.test.ts, organization.service.test.ts, membership.service.test.ts, organization.route.test.ts - zero existing assertions modified.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>None. Write-side infrastructure only, per approved scope - no GET /audit-events, no dashboard, no pagination API.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>One new collection: AuditEvent (actorUserId?, organizationId?, action, entityType, entityId?, outcome, severity, ipAddress?, userAgent?, metadata?, createdAt only - no updatedAt, immutable/append-only). Indexes: {organizationId:1,createdAt:-1}, {actorUserId:1,createdAt:-1}. No TTL (retention deferred as an explicit future policy decision, not silently chosen). No change to any existing collection or index.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Repository exposes create() only - no update/delete/patch/replace exist anywhere in the module. record() (the sole audit.service.ts entry point) never throws regardless of failure origin - best-effort, non-blocking by design, since audit-write failures must never fail the sensitive operation that triggered them; logs a warning via an optional logger parameter when one is supplied. For the three withTransaction()-wrapped SEC-002 operations (createOrganization, changeRole, removeMember), the audit call happens strictly after the transaction resolves, never inside the callback, since MongoDB can retry that callback on a transient error and a non-idempotent audit write is unsafe to duplicate on retry. Metadata is scalar-only (SafeMetadata = Record&lt;string,string|number|boolean|null&gt;) rather than an open Record&lt;string,unknown&gt;, every call site constructs its own small literal object (never a request-body/document spread), and a small case-insensitive forbidden-key backstop (password/passwordhash/token/refreshtoken/accesstoken/secret/cookie) strips anything matching before persisting, as defense-in-depth on top of the explicit-construction discipline. auth.login.failure never populates actorUserId/entityId for any of its four branches, by explicit design, so a targeted account is never misrepresented as a verified actor; the four branches collapse into one action differentiated by metadata.reason, reusing LoginAttemptReason rather than a second taxonomy. LoginAttempt (SEC-001) is completely unchanged and continues to serve its existing throttling-signal purpose alongside the new, separate AuditEvent trail.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35 new tests: audit-event.repository.test.ts (5, including a check that the repository module exports only create()), audit.service.test.ts (7, including forbidden-key stripping and never-throws-on-failure), plus additive tests in auth.service.test.ts (9), organization.service.test.ts (6), membership.service.test.ts (7), and organization.route.test.ts (1 end-to-end spot check) proving each of the 13 instrumented actions produces the correct AuditEvent, that a rolled-back transaction produces none, that a committed transaction only produces one after commit, and that an audit-write failure never fails the primary operation. All using mongodb-memory-server (MongoMemoryServer for the audit module itself; MongoMemoryReplSet for the organizations-side additions, matching those files' existing setup).</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>npm install: 0 new packages (no new dependencies, as required). npm run typecheck: pass on first attempt after implementation. npm run lint: pass on first attempt. npm run format:check: pass after auto-format (files touched by this task only). npm run build: pass. npm run test: 302/302 pass (267 pre-existing + 35 new) - confirmed genuine discovery (33 test files, exact expected count) and zero regression across SEC-001/SEC-002/CAT-001/CAT-002/DB-001/FOUND-002; the optional-trailing-logger-parameter design meant zero of the ~40 pre-existing auth.service.test.ts call sites needed any change to keep passing.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>b10e976</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>organization.reactivated is not instrumented and cannot currently occur - resolveOrganizationContext() blocks every request, including the PATCH that would set status back to ACTIVE, once an organization is SUSPENDED; this is an accepted limitation of SEC-002's own design, not a SEC-003 gap. actorUserId is not populated on any organization-module audit event (organization.created excepted, which does have it) since organization.service.ts/membership.service.ts deliberately received no signature change beyond what already existed - a documented tradeoff, not an oversight. No requestId/correlationId (deferred, no new request-context plumbing introduced). No retention/TTL policy chosen (deferred as an explicit future decision). No read/query API. No SecurityEvent collection, GeoIP, device fingerprinting, or detection/alerting of any kind.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Implements SEC-003 (Audit/security event infrastructure) per the twice-revised, fully approved plan: a single append-only AuditEvent collection wired into exactly the 13 sensitive actions verified reachable in the existing SEC-001/SEC-002 code (organization.reactivated explicitly excluded as unreachable, not manufactured to fill the matrix), audit writes placed strictly after transaction commit (never inside a withTransaction() callback) to avoid duplicate records on MongoDB's automatic retry behavior, best-effort/non-blocking write semantics, locked actor-omission semantics for auth.login.failure, and a three-layer metadata-safety design (scalar-only type, explicit allowlisted construction at every call site, case-insensitive forbidden-key runtime backstop). No modification to modules/catalog, db/, middleware/{authenticate,csrf,rate-limit}.ts, or types/express.d.ts. Nothing pushed to any remote.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -1042,18 +1042,66 @@
           <t>CAT-003</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/catalog/{models/product.model.ts, repositories/product.repository.ts+test, services/product.service.ts+test, validation/product.schema.ts} (6 files, all new).</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/catalog/README.md (added a Product section; existing Category and Brand section text unchanged). No other existing file modified - verified via git diff that category.model.ts, brand.model.ts, category.repository.ts, brand.repository.ts, category.service.ts, brand.service.ts, category.schema.ts, brand.schema.ts, common.schema.ts, slugify.ts, and mongo-errors.ts are all byte-for-byte unchanged.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>None. No HTTP routes/controllers were created - deferred by explicit approved decision, not because SEC-002 is missing (SEC-002 is COMPLETED). Building routes for Product alone while Category/Brand remain routeless would be an inconsistent mid-catalog scope jump, and a Product without any priced Variant (CAT-004 does not exist yet) has limited value exposed via a real API today.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Product collection only (organizationId, name, slug, description, categoryId?, brandId?, media?, status, timestamps). No SKU/barcode/price/compare-at price/cost/inventory/attributes - all explicitly ProductVariant/CAT-004 responsibility per CLAUDE.md section 6.2 and the CAT-004 task row. Indexes: {organizationId, slug} unique, {organizationId, categoryId, status}, {organizationId, brandId, status}.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Every repository function requires organizationId as a mandatory parameter (the same IDOR-prevention convention as Category/Brand). categoryId and brandId are both optional, single (not multi-category), and validated exactly like Category's own assertValidParent: re-fetched scoped by organizationId (a cross-organization reference is indistinguishable from nonexistent) and rejected if the referenced Category/Brand is ARCHIVED - verified by dedicated cross-organization and archived-reference tests for both. A Category/Brand archived AFTER a Product already references it is never cascaded onto the Product - no automatic modification, matching ADR-011's no-cascade principle, verified by a dedicated test. Strict, allowlisted Zod validation - organizationId/_id/__v/createdAt/updatedAt never client-settable. Media is an optional array of {url, altText?}, capped at 10 items by both the Mongoose schema and the Zod schema, reusing the exact same URL-validation depth Brand's own logo.url already uses. Slug uniqueness enforced by a real database unique index, verified by a concurrent-create race test.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>45 new tests: product.repository.test.ts (18 - creation with/without references and media, the 10-media-item cap, organization isolation on findById/findBySlug/list, list filtering by categoryId and by brandId, duplicate slug at DB level, same slug across orgs, concurrent-create race, organizationId immutable on update, explicit-null removes a reference, cross-org update/archive no-ops, archived-still-queryable, index existence/uniqueness), product.service.test.ts (27 - valid creation, optional categoryId/brandId, cross-organization category/brand rejected, nonexistent category/brand rejected, archived category/brand rejected, malformed ObjectId rejected before any DB lookup, auto-slug generation and collision suffixing, explicit duplicate slug rejected, strict-schema rejection on create and update, media URL validation and the 10-item cap, zero-media creation, valid category/brand update, cross-org/archived category update rejected, explicit-null reference removal, archiving a referenced category afterward does NOT cascade onto the product, update allowlist, NotFoundError paths for update/archive). All using mongodb-memory-server (MongoMemoryServer - no transactions needed for product CRUD).</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>npm install: 0 new packages (no new dependencies, as required). npm run typecheck: pass (after fixing one real Mongoose create() type mismatch - see Known Issues). npm run lint: pass on first attempt. npm run format:check: pass after auto-format (files touched by this task only). npm run build: pass. npm run test: 348/348 pass (303 pre-existing + 45 new) - confirmed genuine discovery (35 test files, exact expected count) and zero regression; CAT-001/CAT-002's own 67 tests (38 category + 29 brand) re-run in isolation and confirmed unchanged and passing.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0cb8ca2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>HTTP routes/controllers remain deferred for the whole catalog domain (Category, Brand, and now Product) - an explicit, approved decision, not an oversight, even though SEC-002 (the condition ADR-012 named) is now COMPLETED. No audit-event wiring for the same reason SEC-003 itself gave: catalog has no HTTP-reachable action to audit yet. No multi-category tagging (single categoryId only). Object storage/media upload infrastructure remains unresolved (DEC-006 in OPEN_DECISIONS.md is unrelated; the actual open item is DEC-002, object storage provider) - media is a plain URL reference only, matching Brand's own logo precedent exactly.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Implements CAT-003 (Product foundation) per the approved plan: Product references Category and Brand by ID, both optional, both organization-scoped and non-archived-only at write time (extending Category's own assertValidParent pattern to two cross-collection references instead of a self-reference), with an explicit no-cascade policy once a reference is later archived. No Variant-only field (SKU/barcode/price/cost/inventory/attributes/weight/dimensions/variantIds/hasVariants/defaultVariantId) was added, per CLAUDE.md section 6.2 and the CAT-004 task row. Routes and audit wiring remain deferred by explicit decision. No modification to any CAT-001/CAT-002 file, verified via git diff before committing. No modification to auth/organizations/audit/db/middleware. No new dependencies.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -1109,18 +1109,66 @@
           <t>CAT-004</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/catalog/{models/product-variant.model.ts, repositories/product-variant.repository.ts+test, services/product-variant.service.ts+test, validation/product-variant.schema.ts} (6 files, all new).</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/catalog/README.md (added a ProductVariant section; existing Category/Brand/Product section text unchanged). No other existing file modified - verified via git diff that category.*, brand.*, and all four product.* files (model, repository+test, service+test, schema) are byte-for-byte unchanged.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>None. No HTTP routes/controllers were created - deferred by explicit approved decision, consistent with Category/Brand/Product.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ProductVariant collection (organizationId, productId, sku, barcode?, price, compareAtPrice?, cost?, attributes?, status, timestamps). No currency, media, name/title, or inventory field - all explicitly deferred. Indexes: {organizationId, sku} unique, {organizationId, barcode} unique with partialFilterExpression {barcode:{$exists:true}} (a plain sparse index was tried first and rejected - on a compound index sparse only excludes a document missing ALL indexed fields, and organizationId is always present, so it never excluded a barcode-less variant; a failing test caught this before the fix), {organizationId, productId, status}.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Every repository function requires organizationId as a mandatory parameter (same IDOR-prevention convention as Category/Brand/Product). productId is required and immutable (absent from the update schema entirely, not just nullable) and validated exactly like Product's own assertValidCategory/assertValidBrand: re-fetched scoped by organizationId, rejected if missing/cross-org/ARCHIVED - a variant cannot be newly created under an archived product, but a product archived afterward never cascades onto its existing variants. SKU is required, normalized to uppercase (trim then uppercase) before any duplicate check or persistence, organization-scoped unique, with the database unique index as the ultimate concurrency guarantee (proven by a concurrent-create race test) - a friendly existsWithSku pre-check exists but is not the actual guarantee. Barcode is optional with the same organization-scoped uniqueness, enforced only among variants that actually have one via a partial index. Attributes use an array of {key,value} pairs (never Record&lt;string,unknown&gt;) specifically to structurally rule out prototype pollution; keys are allowlisted to letters/digits/space/hyphen/underscore (blocking Mongo-special $ and . characters) and __proto__/constructor/prototype are explicitly blocked as key values too; duplicate keys (case-insensitive) rejected; capped at 30 items; values restricted to string/number/boolean with null/array/nested-object all rejected. Pricing fields (price required, compareAtPrice/cost optional) are integer minor units per existing ADR-008, validated finite+int+nonnegative to reject NaN/Infinity/-Infinity/negative/fractional values. Strict, allowlisted Zod validation throughout - organizationId/productId/_id/__v/createdAt/updatedAt never client-settable on update.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>59 new tests: product-variant.repository.test.ts (23 - creation with/without optional fields, 30-attribute cap at the model level, organization isolation on findById/findBySku/findByProductId/list, list filtering by productId and status, duplicate SKU and duplicate barcode at DB level, same SKU across orgs, concurrent-create SKU race, two barcode-less variants coexisting under the partial index, immutable organizationId/productId on update, cross-org update/archive no-ops, archived-still-queryable, index existence including the barcode partial filter expression), product-variant.service.test.ts (36 - Product reference validation (cross-org/nonexistent/archived-product rejected, DRAFT-product allowed, malformed productId rejected pre-DB-lookup, no cascade when the product is archived after variant creation), SKU normalization/validation/editability, barcode optionality and non-enforcement of digits-only/checksum, pricing validation (required, zero accepted, negative/fractional/NaN/Infinity rejected, inverted compareAtPrice currently accepted by design), attribute validation (valid cases, duplicate keys, 30-item cap, forbidden __proto__/constructor/prototype keys, a crafted-payload prototype-pollution regression test, Mongo-operator-shaped keys rejected, null/array/nested-object values rejected, whole-array replace on update), strict-schema mass-assignment rejection on create and update, productId immutability, status enum enforcement, unrestricted lifecycle transitions including ARCHIVED-to-ACTIVE, NotFoundError paths). All using mongodb-memory-server (MongoMemoryServer - no transactions needed for variant CRUD).</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>npm install: 0 new packages (no new dependencies, as required). npm run typecheck: pass on first attempt. npm run lint: pass on first attempt. npm run format:check: pass after auto-format (files touched by this task only). npm run build: pass. npm run test: 407/407 pass (348 pre-existing + 59 new) - zero regression; CAT-001/CAT-002/CAT-003's own 102 tests re-run in isolation and confirmed unchanged and passing.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>b98a0ea</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>One real implementation issue found and fixed during testing, not left as a known issue: the barcode index was initially declared with sparse:true, which on a compound index only excludes documents missing ALL indexed fields (organizationId is always present, so it never actually excluded a barcode-less variant) - corrected to a partialFilterExpression:{barcode:{$exists:true}} index instead, matching organization-membership.model.ts's own existing partial-index precedent. HTTP routes/controllers and SEC-003 audit-event wiring both remain deferred for the whole catalog domain, consistent with Category/Brand/Product. No currency field, no variant-specific media, no variant display name/title, no inventory placeholder field, and no compareAtPrice&gt;=price relational rule - all explicitly deferred by locked decision, not oversights.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Implements CAT-004 (ProductVariant foundation) per the approved plan: Variant holds a required, immutable productId reference validated exactly like Product's own Category/Brand reference pattern (organization-scoped, rejects missing/cross-org/archived-at-creation-time, no cascade once created). SKU is the variant's identity (organization-scoped unique, uppercase-normalized, editable, no auto-generation). Barcode is optional with the same uniqueness scope via a partial index. Pricing uses the existing ADR-008 integer-minor-units convention with no new financial architecture. Attributes use a prototype-pollution-safe {key,value}[] array structure instead of Record&lt;string,unknown&gt;, with an explicit key allowlist and a hard cap. No SKU/barcode/price/attributes were added to Product (product.model.ts and all its sibling files are completely untouched), no variantIds/hasVariants/defaultVariantId was added to Product, no inventory field, no variant media, no currency field. Routes and audit wiring remain deferred by explicit decision. Recorded as ADR-021.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -1176,18 +1176,66 @@
           <t>INV-001</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/inventory/{README.md, lib/mongo-errors.ts, models/location.model.ts, models/stock-balance.model.ts, models/inventory-transaction.model.ts, repositories/location.repository.ts+test, repositories/stock-balance.repository.ts+test, repositories/inventory-transaction.repository.ts+test, services/location.service.ts+test, services/inventory.service.ts+test, validation/common.schema.ts, validation/location.schema.ts, validation/inventory-transaction.schema.ts} (18 files, all new).</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>None. No existing file modified - verified via git diff that every CAT-001/002/003/004 file, and every auth/organizations/audit/db/middleware file, is byte-for-byte unchanged.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>None. No HTTP routes/controllers were created - deferred by explicit approved decision, consistent with Category/Brand/Product/ProductVariant.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Three new collections: locations (organizationId, name, code?, status: ACTIVE|ARCHIVED, no DRAFT), stock_balances (organizationId, locationId, variantId, quantityOnHand, updatedAt only - no createdAt), inventory_transactions (organizationId, locationId, variantId, type, quantity, adjustmentDirection?, note?, createdAt only - append-only, no updatedAt). Indexes: locations {organizationId, code} unique partial (code exists); stock_balances {organizationId, locationId, variantId} unique; inventory_transactions {organizationId, variantId, locationId, createdAt desc} and {organizationId, createdAt desc}.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Every repository function requires organizationId as a mandatory parameter (same IDOR-prevention convention as every catalog module). variantId and locationId are validated exactly like ProductVariant's own assertValidProduct: re-fetched scoped by organizationId, rejected if missing/cross-org/ARCHIVED - a new transaction cannot be recorded against an archived variant or location, but archiving either afterward never cascades onto existing balances/history. quantityOnHand is never directly patchable - only two named atomic operations exist (incrementOrCreate, an atomic upsert; decrementIfSufficient, a guarded findOneAndUpdate with the sufficiency check in the filter itself, reusing ADR-018's last-owner-protection pattern in a new domain) - both require an active session, since a balance can only change as part of the single withTransaction() that also writes the corresponding ledger entry. InventoryTransaction is genuinely append-only (create()+list() only, create() requires a session) mirroring audit-event.repository.ts's exact shape. recordTransfer() is a dedicated atomic operation, never two independent recordTransaction() calls, preventing a TRANSFER_OUT/TRANSFER_IN mismatch on partial failure. ADJUSTMENT requires an explicit adjustmentDirection (INCREASE|DECREASE); every other type rejects it, enforced by Zod superRefine plus a Mongoose-layer conditional required function (a plain custom validator does not get invoked for an undefined value, discovered and fixed during testing).</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>76 new tests: location.repository.test.ts (17), stock-balance.repository.test.ts (13, including a dedicated initial-creation and outbound guarded-decrement concurrency test), inventory-transaction.repository.test.ts (11, including immutability and ADJUSTMENT-direction defense-in-depth tests), location.service.test.ts (16), inventory.service.test.ts (25 - variant/location reference validation, quantity type/range validation, ADJUSTMENT direction mapping for every transaction type, negative-stock rejection with full rollback verification, mass-assignment and Mongo-operator-injection rejection, recordTransfer success/insufficient-stock-rollback/same-location-rejection, and the two mandatory concurrency scenarios: two concurrent PURCHASE transactions against a nonexistent balance both succeed with exactly one resulting document and the correct total, and two concurrent SALE 6 against a balance of 10 resolve to exactly one success with a final balance of 4). location/location.service tests use a standalone MongoMemoryServer; stock-balance/inventory-transaction repository tests use a standalone server with mongoose.startSession() (no transaction needed for single-document ops); inventory.service.test.ts uses MongoMemoryReplSet, since recordTransaction()/recordTransfer() genuinely need withTransaction().</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>npm install: 0 new packages (no new dependencies, as required). npm run typecheck: pass (after fixing one real Mongoose validation gap - see Known Issues). npm run lint: pass after removing two unused imports. npm run format:check: pass after auto-format (files touched by this task only). npm run build: pass. npm run test: 488/488 pass (412 pre-existing + 76 new) - zero regression; CAT-001-004's own 166 tests re-run in isolation and confirmed unchanged and passing.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>95105c6</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>One real implementation issue found and fixed during testing: the ADJUSTMENT-requires-direction Mongoose-layer defense-in-depth check was initially written as a single custom path validator, which never fired for the "ADJUSTMENT with no direction" case because Mongoose skips calling plain validators when a path's value is undefined - corrected to a conditional `required` function (which IS evaluated for undefined values) for the "must be present" half, keeping the custom validator only for the "must be absent otherwise" half. HTTP routes/controllers and SEC-003 audit-event wiring both remain deferred, consistent with the whole catalog domain. No currency, no allowNegative/backorder configuration, no reorder points, no forecasting, no cart/checkout/pricing integration, no sourceType/sourceId/orderId/purchaseId/supplierId/saleId - all explicitly deferred by locked decision. A documented future-integration note (not solved here): a later business workflow calling recordTransaction()/recordTransfer() repeatedly may need an idempotency mechanism to prevent duplicate inventory movements on retry.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Implements INV-001 (Inventory engine) per the approved, twice-revised plan: Location/StockBalance/InventoryTransaction as three separate collections (materialized balance kept deliberately separate from the append-only ledger, mirroring SEC-003's single-purpose-collection reasoning), atomic guarded stock mutation extending ADR-018's pattern to a new domain, a dedicated recordTransfer() operation instead of two independent recordTransaction() calls, and explicit ADJUSTMENT direction rather than a bare unsigned-quantity-plus-type mapping. Full multi-location support (including TRANSFER_IN/TRANSFER_OUT) built now, not deferred, since the task's own description names "Locations" explicitly. No SEC-003 integration, no forward-looking foreign keys, no routes - all explicit locked decisions. Recorded as ADR-022.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -1243,18 +1243,66 @@
           <t>CUST-001</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/customers/{README.md, lib/mongo-errors.ts, models/customer.model.ts, models/address.model.ts, repositories/customer.repository.ts+test, repositories/address.repository.ts+test, services/customer.service.ts+test, services/address.service.ts+test, routes/customer.route.ts+test, validation/common.schema.ts, validation/customer.schema.ts, validation/address.schema.ts} (17 files, all new).</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>apps/api/src/routes/v1/index.ts (2 hunks: import + router.use('/customers', ...) mount, mirroring the existing auth/organizations wiring pattern exactly). No other existing file modified.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>New /api/v1/customers/me, /me/addresses, /me/addresses/:id, /me/addresses/:id/default (GET/POST/PATCH/DELETE as applicable) - the first route layer outside SEC-001/SEC-002, approved because authenticate() is already live and a customer managing their own data is inherently a self-service end-user flow. Every handler resolves identity from req.auth.userId only. No staff/admin route; no restore-profile route (not part of the approved route list, though the service/repository function exists and is tested).</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Two new global (non-organization-scoped) collections: customers (userId unique 1:1 with User, firstName, lastName, displayName?, phone?, status ACTIVE|ARCHIVED) and addresses (customerId, recipientName, phone?, line1, line2?, city, state, postalCode, country, isDefaultBilling, isDefaultShipping, status ACTIVE|ARCHIVED). Indexes: customers {userId} unique; addresses {customerId} (listing), {customerId,isDefaultBilling:true} unique partial, {customerId,isDefaultShipping:true} unique partial.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Customer/Address carry no organizationId - an explicit, approved decision based on CUST-001's own SEC-001-only dependency and User's own global (no organizationId) precedent. Every address repository function requires customerId as a mandatory scoping parameter (the same IDOR-prevention convention as every organization-scoped module, anchored on customerId instead). Customer itself has no higher-level tenant object; its own _id, resolved exclusively via findByUserId(req.auth.userId), is the boundary - never accepted as raw client input anywhere. Customer.status and Address default flags are excluded from the general update schemas entirely - only dedicated archive/restore/setDefault functions change them. setDefaultAddress runs inside one withTransaction() (verify ownership+ACTIVE status, unset old default, set new default) per an explicit approved change from the original two-independent-writes plan; the {customerId,isDefaultBilling/isDefaultShipping:true} partial unique indexes remain an additional database-level invariant on top of that transaction. An archived customer cannot create/update/archive/set-default any address (but can still read); an archived address cannot be updated or made default.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>101 new tests: customer.repository.test.ts (15), address.repository.test.ts (17), customer.service.test.ts (21, including a dedicated test proving zero AuditEvent documents are created by any CUST-001 action - see Known Issues), address.service.test.ts (21, including a concurrency test for two simultaneous setDefaultAddress calls targeting different addresses, and a transaction-rollback test proving an archived-target setDefault attempt leaves the prior default untouched), customer.route.test.ts (12, supertest-based, covering the authentication boundary, full profile/address lifecycle, and cross-customer IDOR at the HTTP layer, using MongoMemoryReplSet since the /default route exercises withTransaction()). customer.repository/service and address.repository tests use a standalone MongoMemoryServer; address.service and route tests use MongoMemoryReplSet.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>npm install: 0 new packages (no new dependencies, as required). npm run typecheck: pass on first attempt. npm run lint: pass on first attempt. npm run format:check: pass for all CUST-001 files (one pre-existing, unrelated formatting inconsistency in apps/api/src/modules/inventory/README.md was deliberately left untouched per the explicit "do not modify inventory" boundary for this task - see Known Issues). npm run build: pass. npm run test: 572/572 pass (471 pre-existing + 101 new) - zero regression; CAT-001-004's 166 tests and INV-001's 78 tests re-run in isolation and confirmed unchanged and passing; auth+organizations' 173 tests also re-verified unaffected by the shared routes/v1/index.ts change.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>c3ab6a5</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AUDIT WIRING NOT IMPLEMENTED, FLAGGED FOR A FOLLOW-UP DECISION: the approved customer.archived/customer.restored audit events could not be wired without extending AUDIT_ACTIONS/AUDIT_ENTITY_TYPES in modules/audit/models/audit-event.model.ts, a SEC-003 file - directly conflicting with this task's explicit "do not modify SEC-003" boundary. Resolved by not touching SEC-003 and documenting the conflict (in the module README and a dedicated test proving the current zero-audit-event state) rather than silently picking a side. No restoreCustomerProfile HTTP route exists yet (only the four route paths explicitly approved were added; restore is implemented and tested at the service/repository layer only). A pre-existing, unrelated Prettier formatting inconsistency in apps/api/src/modules/inventory/README.md (present before this task started) was deliberately left uncorrected per the "do not modify inventory" boundary - it causes a repo-wide format:check warning unrelated to CUST-001.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Implements CUST-001 (Customer accounts) per the approved, twice-revised plan: Customer/Address are global entities (no organizationId), Customer.userId is the 1:1 foreign key to User (User itself untouched), Customer.status and Address default flags/status are excluded from general update schemas in favor of dedicated lifecycle/default-setting functions, and setDefaultAddress uses one withTransaction() rather than two independent writes (an approved change from the original plan) with the partial unique indexes as an additional database-level invariant. This is the first module since SEC-001/SEC-002 to add HTTP routes, justified by the self-service nature of the acceptance criterion. No SEC-003 audit wiring (flagged conflict, see Known Issues), no staff/admin APIs, no organization-level customer ownership, no customer ledger, no guest checkout, no orders/cart/payment functionality - all explicitly out of scope per the approved plan. Recorded as ADR-023.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -1310,18 +1310,66 @@
           <t>COM-001</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/wishlist/{README.md, lib/mongo-errors.ts, models/wishlist-item.model.ts, models/back-in-stock-request.model.ts, repositories/wishlist-item.repository.ts+test, repositories/back-in-stock-request.repository.ts+test, services/wishlist.service.ts+test, services/back-in-stock-request.service.ts+test, services/shared-validation.ts, routes/wishlist.route.ts+test, validation/common.schema.ts, validation/wishlist.schema.ts, validation/back-in-stock-request.schema.ts} (18 files, all new).</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>apps/api/src/routes/v1/index.ts (2 hunks: import + router.use(createWishlistRouter(...)) mount with no path prefix, mirroring healthRouter/readyRouter's own no-prefix convention since wishlist.route.ts defines its own top-level /wishlist and /back-in-stock-requests paths). No other existing file modified.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>New GET/POST /api/v1/wishlist, DELETE /api/v1/wishlist/:id, GET/POST /api/v1/back-in-stock-requests, DELETE /api/v1/back-in-stock-requests/:id - self-service, authenticate()-protected, identity always from req.auth.userId. authenticate is scoped via router.use(['/wishlist','/back-in-stock-requests'], authenticate) rather than a blanket call, specifically to avoid intercepting unrelated unmatched routes (a real regression caught by the existing health.route.test.ts test during validation and fixed before completion).</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Two new global-tenant-adjacent collections (organizationId present but not org-owned the way Category/Brand/Product/Variant/Location are - see H14): wishlist_items (customerId, organizationId, variantId, status ACTIVE|ARCHIVED) and back_in_stock_requests (customerId, organizationId, variantId, status PENDING|CANCELLED, no FULFILLED). Indexes: wishlist_items {customerId,variantId} unique partial (status:ACTIVE), {customerId}; back_in_stock_requests {customerId,variantId,status} unique partial (status:PENDING), {customerId}, {organizationId,variantId,status} (forward-justified for a future notification-dispatch task, not speculative).</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>organizationId is present on both collections (a variant reference is only meaningful within a specific organization's catalog) but is never trusted as authorization from the client - validated read-only (exists + ACTIVE) via organizations' existing organizationRepository.findById(), explicitly NOT SEC-002's membership-based resolveOrganizationContext/requirePermission (customers are not organization members). The authoritative tenant check is ProductVariant.findById(organizationId, variantId) itself, which filters by {_id, organizationId} together. Every repository function requires customerId as a mandatory scoping parameter (the customer-analog of the organizationId convention). Partial unique indexes (not plain unique) are required because both collections are soft-deleted: {customerId,variantId} scoped to status:ACTIVE for wishlist, {customerId,variantId,status} scoped to status:PENDING for back-in-stock, each proven by a genuine concurrent-create race test plus an archive/cancel-then-recreate test. Back-in-stock request creation is rejected when aggregate StockBalance.quantityOnHand across all locations for the variant is greater than zero, reusing INV-001's existing, unmodified stock-balance.repository.ts list() as a plain read (not a transaction with the write - a small accepted TOCTOU window, no reservation/backorder behavior invented). An archived customer can still read existing records but cannot create or archive/cancel anything (assertCustomerActive, mirroring CUST-001's own address.service.ts pattern exactly). A new record cannot reference an ARCHIVED variant; an existing record is never cascaded/touched if its variant is archived afterward.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>76 new tests: wishlist-item.repository.test.ts (14) and back-in-stock-request.repository.test.ts (13) on a standalone MongoMemoryServer, including concurrent-duplicate-create races proving the partial unique index (not an application check) is the actual guarantee; wishlist.service.test.ts (18) and back-in-stock-request.service.test.ts (20) covering reference validation (nonexistent/suspended organization, cross-org variant, archived variant), archived-customer write-blocking, cross-customer IDOR, and - for back-in-stock - all four multi-location stock scenarios explicitly required (0/0 allowed, 5/0 rejected, 0/10 rejected, 0/0 allowed again) plus a test proving the stock check never mutates StockBalance itself; wishlist.route.test.ts (11, supertest) covering the authentication boundary, full lifecycle via real HTTP calls, mass-assignment and Mongo-operator-injection rejection, and route-level cross-customer IDOR. No transaction is used anywhere in this module, so no MongoMemoryReplSet is needed even for the route tests.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>npm install: 0 new packages (no new dependencies, as required). npm run typecheck: pass on first attempt. npm run lint: pass on first attempt. npm run format:check: pass for all COM-001 files (the same pre-existing, unrelated apps/api/src/modules/inventory/README.md formatting inconsistency noted in INV-001/CUST-001's own records remains deliberately untouched). npm run build: pass. npm run test: one real regression was found and fixed before this count was reached - see Known Issues. Final: 652/652 pass (576 pre-existing + 76 new) - zero regression; CAT-004's 64, CUST-001's 86, INV-001's 78, SEC-003's 12, and auth+organizations' 173 tests all re-run in isolation and confirmed unchanged and passing.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>183c87d</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>One real implementation issue found and fixed during testing, not left as a known defect: the wishlist router is mounted in routes/v1/index.ts with no path prefix (since its own routes already define top-level /wishlist and /back-in-stock-requests paths, matching healthRouter/readyRouter's convention) - the router initially applied authenticate via a blanket router.use(authenticate), which incorrectly intercepted every request reaching this router in the middleware chain, including a completely unrelated, genuinely unmatched path, and returned 401 instead of letting it fall through to the app's real 404 handler. Caught by the existing health.route.test.ts regression test ("unmatched route returns the standardized 404 envelope") failing during the full-suite run; fixed by scoping the middleware to router.use(['/wishlist','/back-in-stock-requests'], authenticate) before this task was considered complete. No FULFILLED state, no fulfillment detection, no notification delivery (email/SMS/push), no Redis/BullMQ, no reservation/backorder behavior, no staff/admin API, no SEC-003 audit wiring - all explicitly deferred by locked decision, not oversights.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Implements COM-001 (Wishlist and back-in-stock notification requests) per the approved plan: WishlistItem and BackInStockRequest as two separate collections (independent lifecycles, independent partial-unique-index uniqueness rules) rather than one collection with a flag, both carrying organizationId (needed to validate an organization-owned ProductVariant reference) despite Customer itself being global, with organizationId explicitly never trusted as authorization - only the ProductVariant's own organization-scoped lookup is authoritative. Back-in-stock stock semantics reuse INV-001's existing repository unmodified, aggregating across all locations as a plain read. Self-service routes are the second HTTP surface added since SEC-001/SEC-002 (after CUST-001), extending that same precedent. No SEC-003 integration (DEC-007 not reopened), no notification delivery, no FULFILLED state. Recorded as ADR-024.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -1377,18 +1377,66 @@
           <t>COM-002</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/cart/{README.md, lib/mongo-errors.ts, models/cart.model.ts, models/cart-item.model.ts, validation/common.schema.ts, validation/cart-item.schema.ts, repositories/cart.repository.ts+test, repositories/cart-item.repository.ts+test, services/shared-validation.ts, services/cart.service.ts+test, routes/cart.route.ts+test} (14 files, all new).</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>apps/api/src/routes/v1/index.ts (2 hunks: import + router.use('/cart', createCartRouter(...)) mount, matching customers/organizations' own prefixed-mount convention). No other existing file modified.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>New GET /api/v1/cart, POST /api/v1/cart/items, PATCH /api/v1/cart/items/:id, DELETE /api/v1/cart/items/:id, DELETE /api/v1/cart - self-service, authenticate()-protected, identity always from req.auth.userId. Mounted under a '/cart' prefix (unlike wishlist's no-prefix mounting), so a blanket router.use(authenticate) is safe here - every request reaching this router already matched '/cart' in the parent router, avoiding the exact unmatched-route-401 regression class found and fixed in COM-001.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Two new collections: carts (customerId, organizationId, unique {customerId,organizationId}) and cart_items (cartId, organizationId, variantId, quantity 1..9999, unique {cartId,variantId} - a PLAIN unique index, not partial, since CartItem removal is a hard delete). No price/name/SKU/attribute snapshot on CartItem by design - every read resolves the current ProductVariant/Product live.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>organizationId is client-supplied context, never trusted as authorization - validated read-only (exists + ACTIVE) via organizations' existing organizationRepository.findById(), explicitly not SEC-002's membership-based resolveOrganizationContext/requirePermission (customers are not organization members), the same pattern COM-001 established. The authoritative tenant check is ProductVariant.findById(organizationId, variantId) itself. CartItem carries no customerId (by design), so item-level PATCH/DELETE resolve ownership in two steps: look up the item by _id alone, then verify its cartId belongs to a Cart owned by the caller (cartRepository.findById(customerId, item.cartId)) - both "not found" and "belongs to another customer" produce an identical generic 404, no enumeration. GET/DELETE-clear never create a Cart merely from being called (cartRepository.findByCustomerAndOrganization is read-only; only addCartItem calls the atomic findOrCreate). The 9999 per-item quantity ceiling is enforced entirely inside a single atomic MongoDB findOneAndUpdate (filter-embedded ceiling check + $inc + upsert), never via a read-calculate-write sequence, proven by a dedicated concurrent-increment race test. Client can never supply price/subtotal/total/cartId/customerId/status - strict Zod schemas reject all of them; every price/subtotal/total in GET /cart is computed server-side from the current ProductVariant on every call (no snapshot), satisfying "Cart totals are server-authoritative." Cart never mutates StockBalance and never reserves inventory (out-of-stock adds are allowed, quantity is never capped by stock); GET /cart includes an informational inStock flag reusing INV-001's existing, unmodified stock-balance.repository.ts. An ARCHIVED variant blocks new adds and quantity edits (PATCH) but never blocks removal (DELETE), and an existing CartItem is never cascaded/touched when its variant is archived afterward - it simply appears flagged in GET.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>80 new tests: cart.repository.test.ts (12, including a genuine concurrent-findOrCreate race proving the {customerId,organizationId} unique index is the real guarantee) and cart-item.repository.test.ts (17, including two dedicated 9999-ceiling concurrency races: 5000+5000 exceeding the ceiling resolves to exactly one success, and 3000+3000 staying within it applies both) on standalone MongoMemoryServer instances; cart.service.test.ts (35) covering reference validation (nonexistent/suspended organization, cross-org variant, archived variant), archived-customer write-blocking across all four mutating operations, the 9990+9/9990+20 ceiling scenarios at the service layer, dynamic pricing (price changes reflected immediately, no stale snapshot), the informational stock indicator, cross-customer IDOR on update/remove, and mass-assignment/Mongo-operator-injection rejection; cart.route.test.ts (16, supertest) covering the authentication boundary, the full add/get/increment/patch/remove/clear lifecycle via real HTTP, the 9999 ceiling over HTTP, cross-customer and cross-organization isolation, cross-org variant rejection, archived-variant behavior (POST/PATCH reject, DELETE succeeds, GET shows flagged), and a route-mounting regression check confirming an unrelated unmatched route still returns the standard 404 envelope.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>npm install: 0 new packages (no new dependencies, as required). npm run typecheck: pass on first attempt. npm run lint: pass on first attempt. npm run format:check: pass for all COM-002 files after one Prettier --write pass (the same pre-existing, unrelated apps/api/src/modules/inventory/README.md formatting inconsistency noted in every prior task's own record remains deliberately untouched). npm run build: pass. npm run test: 732/732 pass (652 pre-existing + 80 new) - zero regressions; CAT-004's 64, CUST-001's 86, INV-001's 78, SEC-003's 12 (audit), and the new 80 Cart tests all re-run in isolation together (320 tests) and confirmed passing.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5a0639f</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>No Cart status/lifecycle field in this task - no concrete state transition exists yet; a future COM-003 CHECKED_OUT-style transition can be added additively when actually needed. No "list all my carts across every organization" endpoint - not required by the acceptance criteria, deferred by design. No SEC-003 audit wiring - Cart add/update/remove/clear are routine, high-volume self-service actions, the same category already excluded for wishlist and CUST-001's address CRUD. No discounts/tax/shipping/payment calculation - explicitly COM-003+ territory. All by locked decision, not oversights.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Implements COM-002 (Cart lifecycle and server-side pricing validation) per the approved plan: one Cart per (customerId, organizationId), CartItem as a separate hard-deleted collection with no price/name/SKU snapshot (server-computed, always-current pricing/totals), the 9999 per-item quantity ceiling enforced atomically inside the database operation itself (never read-then-write), GET/clear never creating a Cart, and archived-variant handling that blocks new adds/quantity edits but never removal and never cascades. Reuses COM-001's organization/variant validation pattern (read-only org existence+ACTIVE check, no SEC-002 membership) and INV-001's existing, unmodified stock-balance read for an informational availability indicator. Recorded as ADR-025.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -1444,18 +1444,66 @@
           <t>COM-003</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/checkout/{README.md, lib/mongo-errors.ts, validation/common.schema.ts, validation/checkout.schema.ts, services/shared-validation.ts, services/checkout.service.ts+test, routes/checkout.route.ts+test} (9 files, all new); apps/api/src/modules/orders/{README.md, lib/mongo-errors.ts, models/order.model.ts, repositories/order.repository.ts+test} (5 files, all new).</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>apps/api/src/routes/v1/index.ts (2 hunks: import + router.use('/checkout', createCheckoutRouter(...)) mount, matching cart/customers/organizations' own prefixed-mount convention). No CAT-001-004, INV-001, CUST-001, COM-001, COM-002, auth, organizations, audit, or db file modified.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>New POST /api/v1/checkout/preview (read-only) and POST /api/v1/checkout (creates the Order and clears the Cart) - self-service, authenticate()-protected, identity always from req.auth.userId. Both share one internal pricing/validation function so preview and confirm can never drift apart.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>New orders collection (minimal, model+repository only): Order {customerId, organizationId, items[] (embedded OrderItem snapshot: variantId, productId, name, sku, price, quantity, subtotal), subtotal, total, status: PENDING_PAYMENT (only value in this task), shippingAddress/billingAddress (embedded snapshot, not a live reference)}. Deliberately no secondary index (write-only from COM-003's own perspective; COM-004 will add whatever its own order-listing routes need). No CartItem/StockBalance/InventoryTransaction schema change.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>organizationId is client-supplied context, never trusted as authorization - validated read-only (exists + ACTIVE) via organizations' existing organizationRepository.findById(), explicitly not SEC-002's membership middleware (customers are not organization members), the same pattern COM-001/COM-002 established. The authoritative tenant check for every line item is ProductVariant.findById(organizationId, variantId). Every price/name is re-resolved live from the current ProductVariant/Product at both preview and confirm - Cart's own (already dynamic, per ADR-025) totals are never trusted, and the client can never supply price/subtotal/total/status/orderId/cartId/cartItemId (rejected by strict Zod schemas). Every computed monetary value is defensively checked with Number.isSafeInteger before being persisted or returned. Checkout only validates aggregate StockBalance.quantityOnHand (reusing INV-001's existing, unmodified stock-balance.repository.ts) - it never mutates StockBalance and never creates an InventoryTransaction, proven by a dedicated test asserting both are unchanged after a successful checkout. Shipping address is required (explicit id or the customer's own default; both scoped by customerId via the existing, unmodified address.repository.ts, so a foreign customer's address id is indistinguishable from nonexistent); billing falls back to the resolved shipping address when omitted; both are snapshotted into the Order, never a live reference. Order creation and Cart clearing happen inside one withTransaction(), re-reading Cart/CartItem via the transaction's own session by importing COM-002's already-public Cart/CartItem Mongoose models directly (cart.repository.ts/cart-item.repository.ts do not accept a session, and COM-002 is a closed module this task must not modify) - this also means two genuinely concurrent confirm requests for the same cart naturally resolve to exactly one Order via MongoDB's own write-conflict-plus-automatic-retry behavior, with no new idempotency-key infrastructure. A price change between preview and confirm is used silently at confirm, by design - no price lock, no confirmation token. A known, explicitly documented limitation (not solved in this task): a client retry after a lost HTTP response following a successful commit will see an empty cart rather than being replayed the original order.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>52 new tests: order.repository.test.ts (7, on a MongoMemoryReplSet, including transaction commit/rollback participation) and checkout.service.test.ts (34, on a MongoMemoryReplSet) covering customer/organization/address/cart/inventory validation, dynamic pricing (including a price change between preview and confirm used silently), the safe-integer defensive guard, cross-organization variant defense-in-depth, cross-customer IDOR on cart and address, three dedicated transaction tests (forced Order-creation failure leaves the cart uncleared, forced Cart-clearing failure leaves no Order, successful atomic commit of both), and a genuine concurrent-confirm race proving exactly one Order is ever created; checkout.route.test.ts (11, supertest) covering the authentication boundary, the full preview-then-confirm HTTP flow, mass-assignment and Mongo-operator-injection rejection, cross-customer cart and address IDOR at the route layer, and the standard error envelope.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>npm install: 0 new packages (no new dependencies, as required). npm run typecheck: pass on first attempt. npm run lint: pass after removing one unused test binding. npm run format:check: pass for all COM-003 files after one Prettier --write pass (the same pre-existing, unrelated apps/api/src/modules/inventory/README.md formatting inconsistency noted in every prior task's own record remains deliberately untouched). npm run build: pass. npm run test: 784/784 pass (732 pre-existing + 52 new) - zero regressions; CAT-004's 64, CUST-001's 86, INV-001's 78, SEC-003's 12, and COM-002's 80 tests all re-run in isolation together with COM-003's own 52 (372 total) and confirmed unchanged and passing.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>9bd3bfe</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Deliberately deferred by locked decision, not oversights: inventory reservation/decrement (Checkout validates aggregate stock only; no fulfillment-location-selection strategy exists yet for an actual SALE transaction), payment of any kind (DEC-001 payment provider remains OPEN), tax/discount/shipping-cost calculation (Order.total currently equals subtotal, kept as its own field for forward compatibility only), Order lifecycle beyond the initial PENDING_PAYMENT state, cancellation, returns, tracking (all COM-004), a full Idempotency-Key replay mechanism (a genuinely concurrent duplicate confirm is already prevented via the transactional cart-clearing/write-conflict-retry design, but a lost-response client retry after a successful commit is a known, documented, deliberately unsolved gap), and any SEC-003 audit event for checkout/order-creation itself (the Order document is treated as the durable business record; CLAUDE.md's own audit-worthy example list names order cancellation/refund, not plain placement).</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Implements COM-003 (Checkout preview and order creation) per the approved plan: the roadmap's own description ("Checkout preview and order creation") was taken literally - COM-003, not COM-004, creates the first Order, in a new minimal orders module holding only what this task needs (model + a single session-aware create() repository function, no lifecycle service/routes). Preview and confirm share one validation/pricing function; server-authoritative pricing and totals, inventory-validation-only, and atomic Order-creation-plus-Cart-clearing are the three invariants this task was built around, per the approved plan's own final rule. Recorded as ADR-026.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -1511,18 +1511,62 @@
           <t>COM-004</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/returns/{README.md, models/return-request.model.ts, models/return-request-lock.model.ts, repositories/return-request.repository.ts+test, repositories/return-request-lock.repository.ts+test, services/return-request.service.ts+test, services/shared-validation.ts, validation/common.schema.ts, validation/return-request.schema.ts} (all new); apps/api/src/modules/orders/README.md (new; orders module itself pre-existed from COM-003 and was extended, see Files Modified).</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>apps/api/src/modules/orders/{models/order.model.ts, repositories/order.repository.ts+test, services/order.service.ts+test, routes/order.route.ts+test, validation/order.schema.ts, validation/common.schema.ts, services/shared-validation.ts} extended (order.model.ts/order.repository.ts pre-existed from COM-003, additively extended - create() untouched); apps/api/src/modules/audit/models/audit-event.model.ts (additive: +order.status_changed, +order.cancelled, +return.requested AUDIT_ACTIONS, +Order, +ReturnRequest AUDIT_ENTITY_TYPES); apps/api/src/routes/v1/index.ts (mount the new orders router). No CAT-001-004, INV-001, CUST-001, COM-001, COM-002, COM-003 checkout files, auth, organizations, or db file modified.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>New GET /api/v1/orders, GET /api/v1/orders/:id, POST /api/v1/orders/:id/cancel, GET /api/v1/orders/:id/returns, POST /api/v1/orders/:id/returns - all self-service, authenticate()-protected, identity always from req.auth.userId, every query scoped by the resolved customerId. confirmOrder/startProcessing/markPacked/markShipped/markDelivered are implemented and tested but exposed via zero HTTP routes in this tranche (no staff/admin API, no SEC-002 permission extension) - confirmOrder is the documented internal boundary a future COM-005 will call once a payment webhook is verified.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Order gained ORDER_STATUSES (PENDING_PAYMENT, CONFIRMED, PROCESSING, PACKED, SHIPPED, DELIVERED, CANCELLED), cancellationReason/cancelledAt, carrier/trackingNumber/shippedAt/deliveredAt, and indexes {customerId,createdAt:-1}/{organizationId,status}. New ReturnRequest collection (orderId, customerId, organizationId, items[{variantId,quantity}], reason, status: PENDING|APPROVED|REJECTED|RECEIVED - only PENDING reachable this tranche, requestedAt), indexes {orderId}/{customerId,createdAt:-1}. New ReturnRequestLock collection (orderId, createdAt), unique index {orderId} - a pure serialization point with no stored counter, used only as an atomic contention point inside the return-request transaction.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Every Order/ReturnRequest status transition is enforced by an atomically-guarded findOneAndUpdate whose filter embeds the required current status/quantity ceiling - never read-then-write. Return-quantity integrity against concurrent/overlapping submissions is protected by ReturnRequestLock, atomically upserted inside the withTransaction() callback before the aggregate read, forcing MongoDB's own write-conflict detection and the driver's automatic retry to serialize concurrent inserts against the same order - proven by two dedicated concurrency tests. The mandatory post-implementation security review found one HIGH finding, F-1: a single return-request payload repeating the same variantId bypassed the purchased-quantity/cumulative-quantity invariant, since both the Order-snapshot check and the in-transaction cumulative check validated each item entry independently instead of by aggregate. Remediated with schema-level duplicate-variantId rejection (case-insensitive) plus independent service-layer per-variant quantity aggregation, so the invariant holds even if the schema guarantee were ever weakened - the service does not rely solely on schema validation. An independent follow-up security review re-verified the fix (fresh diff trace, fresh schema probes, re-run of both concurrency tests, full regression suite) and returned PASS with no new findings. Cross-customer IDOR proven impossible on every Order/ReturnRequest lookup (identical generic 404). No staff/admin order APIs, no SEC-002 permission extension, and zero StockBalance/InventoryTransaction writes (proven by a dedicated negative test) in this tranche.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>139 new tests total: orders/repositories (25), orders/services (31), orders/routes (20), returns/repositories (8), returns/repositories lock (4), returns/services (29 initial + 4 F-1 regression = 33), including two mandatory concurrency scenarios proven against a real MongoDB replica set (two simultaneous overlapping return requests cannot together exceed the purchased quantity, verified via an explicit aggregation of the persisted total, not merely a promise-rejection count; two simultaneous non-overlapping return requests both succeed).</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>npm install: 0 new packages. npm run typecheck: pass. npm run lint: pass. npm run format:check: pass for all COM-004 files (2 known pre-existing, unrelated warnings remain in apps/api/src/modules/checkout/README.md and apps/api/src/modules/inventory/README.md, noted in every prior task record since COM-003). npm run build: pass across all 4 workspaces. npm run test: 891/891 pass (zero regression) - independently re-run twice: once for the Tranche A implementation (891/891 before the F-1 finding, counts differ slightly across the review/remediation/follow-up turns as the 4 new regression tests were added) and again, fresh, after the F-1 remediation and its independent follow-up security review, both confirming 891/891.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5af12bd (Tranche A implementation), 43d1af1 (F-1 remediation)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Tranche B explicitly deferred, not an oversight: staff/admin order management (confirm/process/pack/ship/deliver routes, staff cancellation from PROCESSING - blocked on a SEC-002 ORDER_READ/ORDER_MANAGE permission extension that does not exist yet), return approval/rejection/receipt, fulfillment-location assignment and any inventory decrement/restock (Order/OrderItem still carry no locationId), payment and refund integration (DEC-001 remains OPEN), and return-window enforcement (no duration defined by any existing Planning/ADR evidence). COM-004 is recorded as IN_PROGRESS, not COMPLETED, pending Tranche B.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Implements COM-004 (Order lifecycle, tracking, cancellation and returns) Tranche A per the approved plan: customer-facing order state machine, cancellation, tracking fields, and return request creation/listing. The approved plan explicitly excluded staff/admin APIs, payment/refund, inventory mutation, and return-window enforcement from this tranche. A HIGH-severity finding (F-1) surfaced by the mandatory security review was remediated and independently re-verified PASS before this record was written, per the explicit instruction that Planning/completion records be held back until the security-review workflow passes. orders/README.md and returns/README.md reference an architecture decision ADR-027, which has not yet been added to ARCHITECTURE_DECISIONS.md - a known, flagged gap, left untouched in this update since recording architecture decisions was outside this closure task's approved scope.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">

--- a/Planning/DEVELOPMENT_PROGRESS.xlsx
+++ b/Planning/DEVELOPMENT_PROGRESS.xlsx
@@ -1564,7 +1564,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Implements COM-004 (Order lifecycle, tracking, cancellation and returns) Tranche A per the approved plan: customer-facing order state machine, cancellation, tracking fields, and return request creation/listing. The approved plan explicitly excluded staff/admin APIs, payment/refund, inventory mutation, and return-window enforcement from this tranche. A HIGH-severity finding (F-1) surfaced by the mandatory security review was remediated and independently re-verified PASS before this record was written, per the explicit instruction that Planning/completion records be held back until the security-review workflow passes. orders/README.md and returns/README.md reference an architecture decision ADR-027, which has not yet been added to ARCHITECTURE_DECISIONS.md - a known, flagged gap, left untouched in this update since recording architecture decisions was outside this closure task's approved scope.</t>
+          <t>Implements COM-004 (Order lifecycle, tracking, cancellation and returns) Tranche A per the approved plan: customer-facing order state machine, cancellation, tracking fields, and return request creation/listing. The approved plan explicitly excluded staff/admin APIs, payment/refund, inventory mutation, and return-window enforcement from this tranche. A HIGH-severity finding (F-1) surfaced by the mandatory security review was remediated and independently re-verified PASS before this record was written, per the explicit instruction that Planning/completion records be held back until the security-review workflow passes. Recorded as ADR-027 ("Order Lifecycle State Machine and Return Request Foundation (COM-004 Tranche A)") in ARCHITECTURE_DECISIONS.md. orders/README.md's own ADR-027 citations are valid now that the entry exists; returns/README.md was re-checked and does not reference any ADR number (correcting an inaccurate note in this cell's earlier version, which claimed it did).</t>
         </is>
       </c>
     </row>
